--- a/ITech/Products.xlsx
+++ b/ITech/Products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workspace\GraduationProject\ITech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D54FBF-B07A-4C82-8294-AF274DBE2BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E19B04-3671-4918-BB37-0877C82B75B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>Image1Name</t>
   </si>
@@ -78,106 +78,16 @@
     <t>CategoryId</t>
   </si>
   <si>
-    <t>IT-CSV-1</t>
-  </si>
-  <si>
-    <t>IT-CSV-1-img-1</t>
-  </si>
-  <si>
-    <t>IT-CSV-1-img-2</t>
-  </si>
-  <si>
-    <t>IT-CSV-1-img-3</t>
-  </si>
-  <si>
-    <t>IT-CSV-1-img-4</t>
-  </si>
-  <si>
-    <t>IT-CSV-1-img-5</t>
-  </si>
-  <si>
-    <t>IT-CSV-1-img-6</t>
-  </si>
-  <si>
-    <t>IT-CSV-1-img-7</t>
-  </si>
-  <si>
-    <t>IT-CSV-1-img-8</t>
-  </si>
-  <si>
-    <t>Nokia C1 - 5.45-inch 16GB/1GB Dual SIM 3G Mobile Phone - Charcoal</t>
-  </si>
-  <si>
-    <t>Nokia</t>
-  </si>
-  <si>
-    <t>fasdfasdf</t>
-  </si>
-  <si>
-    <t>IT-CSV-2</t>
-  </si>
-  <si>
-    <t>IT-CSV-2-img-1</t>
-  </si>
-  <si>
-    <t>IT-CSV-2-img-2</t>
-  </si>
-  <si>
-    <t>IT-CSV-2-img-3</t>
-  </si>
-  <si>
-    <t>IT-CSV-2-img-4</t>
-  </si>
-  <si>
-    <t>IT-CSV-2-img-5</t>
-  </si>
-  <si>
-    <t>IT-CSV-2-img-6</t>
-  </si>
-  <si>
-    <t>IT-CSV-2-img-7</t>
-  </si>
-  <si>
-    <t>IT-CSV-2-img-8</t>
-  </si>
-  <si>
-    <t>XIAOMI Redmi 9T - 6.53-inch 128GB/6GB Dual SIM Mobile Phone - Twilight Blue</t>
-  </si>
-  <si>
-    <t>asdfdf</t>
-  </si>
-  <si>
-    <t>IT-CSV-3</t>
-  </si>
-  <si>
-    <t>IT-CSV-3-img-1</t>
-  </si>
-  <si>
-    <t>IT-CSV-3-img-2</t>
-  </si>
-  <si>
-    <t>IT-CSV-3-img-3</t>
-  </si>
-  <si>
-    <t>IT-CSV-3-img-4</t>
-  </si>
-  <si>
-    <t>IT-CSV-3-img-5</t>
-  </si>
-  <si>
-    <t>IT-CSV-3-img-6</t>
-  </si>
-  <si>
-    <t>IT-CSV-3-img-7</t>
-  </si>
-  <si>
-    <t>IT-CSV-3-img-8</t>
-  </si>
-  <si>
-    <t>Samsung Galaxy A12 - 6.5-inch 64GB/4GB Dual SIM Mobile Phone - Blue</t>
-  </si>
-  <si>
-    <t>trytytyy</t>
+    <t>Samsung Galaxy A72 - 6.7-inch 128GB/8GB Dual SIM Mobile Phone - Awesome Black</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>XIAOMI Redmi 10 - 6.5-inch 128GB/6GB Dual SIM Mobile Phone - Sea Blue</t>
+  </si>
+  <si>
+    <t>empty</t>
   </si>
 </sst>
 </file>
@@ -227,11 +137,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,346 +484,1154 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="str">
+        <f>CONCATENATE("IT-CSV-",ROW()-1)</f>
+        <v>IT-CSV-1</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <f t="shared" ref="B2:B31" si="0">CONCATENATE(A2,"-img-",1)</f>
+        <v>IT-CSV-1-img-1</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f t="shared" ref="C2:C31" si="1">CONCATENATE(A2,"-img-",2)</f>
+        <v>IT-CSV-1-img-2</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <f t="shared" ref="D2:D31" si="2">CONCATENATE(A2,"-img-",3)</f>
+        <v>IT-CSV-1-img-3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="K2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="L2" s="4">
+        <v>7799</v>
+      </c>
+      <c r="M2" t="s">
         <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2">
-        <v>1055</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
       </c>
       <c r="N2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3">
-        <v>3450</v>
-      </c>
-      <c r="M3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
+      <c r="A3" s="2" t="str">
+        <f>CONCATENATE("IT-CSV-",ROW()-1)</f>
+        <v>IT-CSV-2</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-2-img-1</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-2-img-2</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-2-img-3</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <f t="shared" ref="E2:E31" si="3">CONCATENATE(A3,"-img-",4)</f>
+        <v>IT-CSV-2-img-4</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <f t="shared" ref="F2:F31" si="4">CONCATENATE(A3,"-img-",5)</f>
+        <v>IT-CSV-2-img-5</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G2:G31" si="5">CONCATENATE(A3,"-img-",6)</f>
+        <v>IT-CSV-2-img-6</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H2:H31" si="6">CONCATENATE(A3,"-img-",7)</f>
+        <v>IT-CSV-2-img-7</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I2:I31" si="7">CONCATENATE(A3,"-img-",8)</f>
+        <v>IT-CSV-2-img-8</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4">
-        <v>2777</v>
-      </c>
-      <c r="M4" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
+      <c r="A4" s="2" t="str">
+        <f t="shared" ref="A4:A31" si="8">CONCATENATE("IT-CSV-",ROW()-1)</f>
+        <v>IT-CSV-3</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-3-img-1</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-3-img-2</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-3-img-3</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-3-img-4</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-3-img-5</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-3-img-6</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-3-img-7</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-3-img-8</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="A5" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-4</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-4-img-1</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-4-img-2</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-4-img-3</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-4-img-4</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-4-img-5</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-4-img-6</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-4-img-7</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-4-img-8</v>
+      </c>
     </row>
     <row r="6" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="A6" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-5</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-5-img-1</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-5-img-2</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-5-img-3</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-5-img-4</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-5-img-5</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-5-img-6</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-5-img-7</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-5-img-8</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="A7" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-6</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-6-img-1</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-6-img-2</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-6-img-3</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-6-img-4</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-6-img-5</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-6-img-6</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-6-img-7</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-6-img-8</v>
+      </c>
     </row>
     <row r="8" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="A8" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-7</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-7-img-1</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-7-img-2</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-7-img-3</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-7-img-4</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-7-img-5</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-7-img-6</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-7-img-7</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-7-img-8</v>
+      </c>
     </row>
     <row r="9" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="A9" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-8</v>
+      </c>
+      <c r="B9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-8-img-1</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-8-img-2</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-8-img-3</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-8-img-4</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-8-img-5</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-8-img-6</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-8-img-7</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-8-img-8</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-9</v>
+      </c>
+      <c r="B10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-9-img-1</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-9-img-2</v>
+      </c>
+      <c r="D10" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-9-img-3</v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-9-img-4</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-9-img-5</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-9-img-6</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-9-img-7</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-9-img-8</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="A11" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-10</v>
+      </c>
+      <c r="B11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-10-img-1</v>
+      </c>
+      <c r="C11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-10-img-2</v>
+      </c>
+      <c r="D11" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-10-img-3</v>
+      </c>
+      <c r="E11" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-10-img-4</v>
+      </c>
+      <c r="F11" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-10-img-5</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-10-img-6</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-10-img-7</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-10-img-8</v>
+      </c>
     </row>
     <row r="12" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="A12" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-11</v>
+      </c>
+      <c r="B12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-11-img-1</v>
+      </c>
+      <c r="C12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-11-img-2</v>
+      </c>
+      <c r="D12" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-11-img-3</v>
+      </c>
+      <c r="E12" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-11-img-4</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-11-img-5</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-11-img-6</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-11-img-7</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-11-img-8</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="A13" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-12</v>
+      </c>
+      <c r="B13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-12-img-1</v>
+      </c>
+      <c r="C13" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-12-img-2</v>
+      </c>
+      <c r="D13" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-12-img-3</v>
+      </c>
+      <c r="E13" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-12-img-4</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-12-img-5</v>
+      </c>
+      <c r="G13" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-12-img-6</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-12-img-7</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-12-img-8</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="A14" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-13</v>
+      </c>
+      <c r="B14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-13-img-1</v>
+      </c>
+      <c r="C14" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-13-img-2</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-13-img-3</v>
+      </c>
+      <c r="E14" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-13-img-4</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-13-img-5</v>
+      </c>
+      <c r="G14" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-13-img-6</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-13-img-7</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-13-img-8</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="A15" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-14</v>
+      </c>
+      <c r="B15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-14-img-1</v>
+      </c>
+      <c r="C15" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-14-img-2</v>
+      </c>
+      <c r="D15" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-14-img-3</v>
+      </c>
+      <c r="E15" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-14-img-4</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-14-img-5</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-14-img-6</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-14-img-7</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-14-img-8</v>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="A16" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-15</v>
+      </c>
+      <c r="B16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-15-img-1</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-15-img-2</v>
+      </c>
+      <c r="D16" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-15-img-3</v>
+      </c>
+      <c r="E16" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-15-img-4</v>
+      </c>
+      <c r="F16" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-15-img-5</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-15-img-6</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-15-img-7</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-15-img-8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-16</v>
+      </c>
+      <c r="B17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-16-img-1</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-16-img-2</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-16-img-3</v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-16-img-4</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-16-img-5</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-16-img-6</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-16-img-7</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-16-img-8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-17</v>
+      </c>
+      <c r="B18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-17-img-1</v>
+      </c>
+      <c r="C18" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-17-img-2</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-17-img-3</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-17-img-4</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-17-img-5</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-17-img-6</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-17-img-7</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-17-img-8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-18</v>
+      </c>
+      <c r="B19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-18-img-1</v>
+      </c>
+      <c r="C19" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-18-img-2</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-18-img-3</v>
+      </c>
+      <c r="E19" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-18-img-4</v>
+      </c>
+      <c r="F19" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-18-img-5</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-18-img-6</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-18-img-7</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-18-img-8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-19</v>
+      </c>
+      <c r="B20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-19-img-1</v>
+      </c>
+      <c r="C20" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-19-img-2</v>
+      </c>
+      <c r="D20" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-19-img-3</v>
+      </c>
+      <c r="E20" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-19-img-4</v>
+      </c>
+      <c r="F20" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-19-img-5</v>
+      </c>
+      <c r="G20" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-19-img-6</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-19-img-7</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-19-img-8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-20</v>
+      </c>
+      <c r="B21" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-20-img-1</v>
+      </c>
+      <c r="C21" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-20-img-2</v>
+      </c>
+      <c r="D21" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-20-img-3</v>
+      </c>
+      <c r="E21" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-20-img-4</v>
+      </c>
+      <c r="F21" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-20-img-5</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-20-img-6</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-20-img-7</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-20-img-8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-21</v>
+      </c>
+      <c r="B22" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-21-img-1</v>
+      </c>
+      <c r="C22" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-21-img-2</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-21-img-3</v>
+      </c>
+      <c r="E22" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-21-img-4</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-21-img-5</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-21-img-6</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-21-img-7</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-21-img-8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-22</v>
+      </c>
+      <c r="B23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-22-img-1</v>
+      </c>
+      <c r="C23" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-22-img-2</v>
+      </c>
+      <c r="D23" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-22-img-3</v>
+      </c>
+      <c r="E23" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-22-img-4</v>
+      </c>
+      <c r="F23" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-22-img-5</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-22-img-6</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-22-img-7</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-22-img-8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-23</v>
+      </c>
+      <c r="B24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-23-img-1</v>
+      </c>
+      <c r="C24" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-23-img-2</v>
+      </c>
+      <c r="D24" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-23-img-3</v>
+      </c>
+      <c r="E24" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-23-img-4</v>
+      </c>
+      <c r="F24" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-23-img-5</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-23-img-6</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-23-img-7</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-23-img-8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-24</v>
+      </c>
+      <c r="B25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-24-img-1</v>
+      </c>
+      <c r="C25" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-24-img-2</v>
+      </c>
+      <c r="D25" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-24-img-3</v>
+      </c>
+      <c r="E25" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-24-img-4</v>
+      </c>
+      <c r="F25" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-24-img-5</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-24-img-6</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-24-img-7</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-24-img-8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-25</v>
+      </c>
+      <c r="B26" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-25-img-1</v>
+      </c>
+      <c r="C26" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-25-img-2</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-25-img-3</v>
+      </c>
+      <c r="E26" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-25-img-4</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-25-img-5</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-25-img-6</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-25-img-7</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-25-img-8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-26</v>
+      </c>
+      <c r="B27" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-26-img-1</v>
+      </c>
+      <c r="C27" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-26-img-2</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-26-img-3</v>
+      </c>
+      <c r="E27" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-26-img-4</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-26-img-5</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-26-img-6</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-26-img-7</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-26-img-8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-27</v>
+      </c>
+      <c r="B28" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-27-img-1</v>
+      </c>
+      <c r="C28" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-27-img-2</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-27-img-3</v>
+      </c>
+      <c r="E28" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-27-img-4</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-27-img-5</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-27-img-6</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-27-img-7</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-27-img-8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-28</v>
+      </c>
+      <c r="B29" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-28-img-1</v>
+      </c>
+      <c r="C29" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-28-img-2</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-28-img-3</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-28-img-4</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-28-img-5</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-28-img-6</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-28-img-7</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-28-img-8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-29</v>
+      </c>
+      <c r="B30" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-29-img-1</v>
+      </c>
+      <c r="C30" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-29-img-2</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-29-img-3</v>
+      </c>
+      <c r="E30" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-29-img-4</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-29-img-5</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-29-img-6</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-29-img-7</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-29-img-8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>IT-CSV-30</v>
+      </c>
+      <c r="B31" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IT-CSV-30-img-1</v>
+      </c>
+      <c r="C31" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-CSV-30-img-2</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>IT-CSV-30-img-3</v>
+      </c>
+      <c r="E31" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>IT-CSV-30-img-4</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>IT-CSV-30-img-5</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="5"/>
+        <v>IT-CSV-30-img-6</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="6"/>
+        <v>IT-CSV-30-img-7</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="7"/>
+        <v>IT-CSV-30-img-8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
